--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_BALONCESTO TELDE.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_BALONCESTO TELDE.xlsx
@@ -565,13 +565,13 @@
         <v>24</v>
       </c>
       <c r="D2" t="n">
-        <v>26.9083</v>
+        <v>12.6763</v>
       </c>
       <c r="E2" t="n">
-        <v>42.3562</v>
+        <v>30.4493</v>
       </c>
       <c r="F2" t="n">
-        <v>-15.448</v>
+        <v>-17.7734</v>
       </c>
       <c r="G2" t="n">
         <v>6.264</v>
@@ -610,13 +610,13 @@
         <v>16.6868</v>
       </c>
       <c r="S2" t="n">
-        <v>19.2125</v>
+        <v>4.9806</v>
       </c>
       <c r="T2" t="n">
-        <v>14.3388</v>
+        <v>2.4318</v>
       </c>
       <c r="U2" t="n">
-        <v>4.8737</v>
+        <v>2.5489</v>
       </c>
       <c r="V2" t="n">
         <v>-4.001600000000001</v>
@@ -643,13 +643,13 @@
         <v>18</v>
       </c>
       <c r="D3" t="n">
-        <v>24.6369</v>
+        <v>6.526300000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>12.6429</v>
+        <v>-3.6683</v>
       </c>
       <c r="F3" t="n">
-        <v>11.9939</v>
+        <v>10.1946</v>
       </c>
       <c r="G3" t="n">
         <v>1.745299999999999</v>
@@ -688,13 +688,13 @@
         <v>33.9555</v>
       </c>
       <c r="S3" t="n">
-        <v>19.9491</v>
+        <v>1.8383</v>
       </c>
       <c r="T3" t="n">
-        <v>18.2707</v>
+        <v>1.9594</v>
       </c>
       <c r="U3" t="n">
-        <v>1.6784</v>
+        <v>-0.1210000000000002</v>
       </c>
       <c r="V3" t="n">
         <v>0.2254999999999999</v>
@@ -721,13 +721,13 @@
         <v>25</v>
       </c>
       <c r="D4" t="n">
-        <v>6.4226</v>
+        <v>3.4916</v>
       </c>
       <c r="E4" t="n">
-        <v>9.7803</v>
+        <v>11.3527</v>
       </c>
       <c r="F4" t="n">
-        <v>-3.357500000000001</v>
+        <v>-7.860799999999998</v>
       </c>
       <c r="G4" t="n">
         <v>2.4943</v>
@@ -766,13 +766,13 @@
         <v>52.0006</v>
       </c>
       <c r="S4" t="n">
-        <v>2.294100000000001</v>
+        <v>-0.6372999999999998</v>
       </c>
       <c r="T4" t="n">
-        <v>-5.6852</v>
+        <v>-4.113</v>
       </c>
       <c r="U4" t="n">
-        <v>7.979</v>
+        <v>3.4755</v>
       </c>
       <c r="V4" t="n">
         <v>16.9631</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.2696</v>
+        <v>1.7057</v>
       </c>
       <c r="E5" t="n">
-        <v>2.1534</v>
+        <v>1.753</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1162</v>
+        <v>-0.0473</v>
       </c>
       <c r="G5" t="n">
         <v>1.0327</v>
@@ -844,13 +844,13 @@
         <v>0.3881</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8488</v>
+        <v>0.2849</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4856</v>
+        <v>0.0852</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3632</v>
+        <v>0.1996</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>1.831</v>
+        <v>1.6218</v>
       </c>
       <c r="E6" t="n">
-        <v>1.5643</v>
+        <v>1.4642</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2667</v>
+        <v>0.1577</v>
       </c>
       <c r="G6" t="n">
         <v>1.1522</v>
@@ -922,13 +922,13 @@
         <v>1.1642</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4847</v>
+        <v>0.2756999999999999</v>
       </c>
       <c r="T6" t="n">
-        <v>0.6808</v>
+        <v>0.5807</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1961</v>
+        <v>-0.305</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.3822</v>
+        <v>-0.355</v>
       </c>
       <c r="E7" t="n">
         <v>-0.7279</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3457</v>
+        <v>0.3729</v>
       </c>
       <c r="G7" t="n">
         <v>-0.4004</v>
@@ -1000,13 +1000,13 @@
         <v>0.194</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1759</v>
+        <v>-0.1486</v>
       </c>
       <c r="T7" t="n">
         <v>-0.0606</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1153</v>
+        <v>-0.08799999999999999</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.4795</v>
+        <v>-0.5736</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.0593</v>
+        <v>-1.0988</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5797</v>
+        <v>0.5252</v>
       </c>
       <c r="G8" t="n">
         <v>0.02060000000000001</v>
@@ -1078,13 +1078,13 @@
         <v>0.3881</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5581</v>
+        <v>0.464</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3892</v>
+        <v>0.3496</v>
       </c>
       <c r="U8" t="n">
-        <v>0.169</v>
+        <v>0.1144</v>
       </c>
       <c r="V8" t="n">
         <v>-0.2821</v>
@@ -1111,13 +1111,13 @@
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.6883</v>
+        <v>-4.1516</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.2556</v>
+        <v>-3.8552</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4326</v>
+        <v>-0.2963999999999999</v>
       </c>
       <c r="G9" t="n">
         <v>-2.8534</v>
@@ -1156,13 +1156,13 @@
         <v>0.388</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.3885</v>
+        <v>-0.8518999999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5450999999999999</v>
+        <v>-0.1447</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.8434</v>
+        <v>-0.7071000000000001</v>
       </c>
       <c r="V9" t="n">
         <v>0.3299</v>
@@ -1189,13 +1189,13 @@
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.384499999999999</v>
+        <v>-4.7933</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.9804</v>
+        <v>-2.58</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.4041</v>
+        <v>-2.2133</v>
       </c>
       <c r="G10" t="n">
         <v>-5.1239</v>
@@ -1234,13 +1234,13 @@
         <v>0.9701</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.4845</v>
+        <v>-0.8935</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.2114</v>
+        <v>-0.8110000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2732</v>
+        <v>-0.08250000000000002</v>
       </c>
       <c r="V10" t="n">
         <v>1.2239</v>
@@ -1267,13 +1267,13 @@
         <v>18</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.815400000000001</v>
+        <v>-11.2366</v>
       </c>
       <c r="E11" t="n">
-        <v>0.5709999999999988</v>
+        <v>-3.6886</v>
       </c>
       <c r="F11" t="n">
-        <v>-6.386100000000001</v>
+        <v>-7.547599999999999</v>
       </c>
       <c r="G11" t="n">
         <v>-13.6704</v>
@@ -1312,13 +1312,13 @@
         <v>19.9855</v>
       </c>
       <c r="S11" t="n">
-        <v>6.7177</v>
+        <v>1.2966</v>
       </c>
       <c r="T11" t="n">
-        <v>5.5178</v>
+        <v>1.2581</v>
       </c>
       <c r="U11" t="n">
-        <v>1.2002</v>
+        <v>0.03860000000000002</v>
       </c>
       <c r="V11" t="n">
         <v>-4.6835</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>D. VAZQUEZ JEREZ</t>
+          <t>A. SANTANA OJEDA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D12" t="n">
-        <v>-14.8245</v>
+        <v>-11.7205</v>
       </c>
       <c r="E12" t="n">
-        <v>-16.6937</v>
+        <v>-6.422400000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>1.869</v>
+        <v>-5.2977</v>
       </c>
       <c r="G12" t="n">
-        <v>-20.7961</v>
+        <v>-6.6041</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.3389</v>
+        <v>1.3478</v>
       </c>
       <c r="I12" t="n">
-        <v>-19.4574</v>
+        <v>-7.951700000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>2.158799999999999</v>
+        <v>17.7209</v>
       </c>
       <c r="K12" t="n">
-        <v>8.0124</v>
+        <v>12.3251</v>
       </c>
       <c r="L12" t="n">
-        <v>-5.853800000000001</v>
+        <v>5.3959</v>
       </c>
       <c r="M12" t="n">
-        <v>-22.9544</v>
+        <v>-24.325</v>
       </c>
       <c r="N12" t="n">
-        <v>-9.351099999999999</v>
+        <v>-10.9774</v>
       </c>
       <c r="O12" t="n">
-        <v>-13.6031</v>
+        <v>-13.3471</v>
       </c>
       <c r="P12" t="n">
-        <v>3.6864</v>
+        <v>-3.1045</v>
       </c>
       <c r="Q12" t="n">
-        <v>-29.299</v>
+        <v>-35.1199</v>
       </c>
       <c r="R12" t="n">
-        <v>32.9854</v>
+        <v>32.0156</v>
       </c>
       <c r="S12" t="n">
-        <v>7.5156</v>
+        <v>-4.8659</v>
       </c>
       <c r="T12" t="n">
-        <v>5.4646</v>
+        <v>-6.1537</v>
       </c>
       <c r="U12" t="n">
-        <v>2.0505</v>
+        <v>1.2876</v>
       </c>
       <c r="V12" t="n">
-        <v>-5.2301</v>
+        <v>2.854</v>
       </c>
       <c r="W12" t="n">
-        <v>4.982100000000001</v>
+        <v>17.1301</v>
       </c>
       <c r="X12" t="n">
-        <v>-10.2122</v>
+        <v>-14.276</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. SANTANA OJEDA</t>
+          <t>P. SÁNCHEZ GUTIERREZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>26</v>
       </c>
       <c r="D13" t="n">
-        <v>-25.1025</v>
+        <v>-14.0431</v>
       </c>
       <c r="E13" t="n">
-        <v>-17.4014</v>
+        <v>-9.506100000000002</v>
       </c>
       <c r="F13" t="n">
-        <v>-7.700999999999999</v>
+        <v>-4.537</v>
       </c>
       <c r="G13" t="n">
-        <v>-6.6041</v>
+        <v>1.0546</v>
       </c>
       <c r="H13" t="n">
-        <v>1.3478</v>
+        <v>7.057799999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>-7.951700000000001</v>
+        <v>-6.0031</v>
       </c>
       <c r="J13" t="n">
-        <v>17.7209</v>
+        <v>30.363</v>
       </c>
       <c r="K13" t="n">
-        <v>12.3251</v>
+        <v>23.1633</v>
       </c>
       <c r="L13" t="n">
-        <v>5.3959</v>
+        <v>7.199800000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>-24.325</v>
+        <v>-29.3085</v>
       </c>
       <c r="N13" t="n">
-        <v>-10.9774</v>
+        <v>-16.1055</v>
       </c>
       <c r="O13" t="n">
-        <v>-13.3471</v>
+        <v>-13.2028</v>
       </c>
       <c r="P13" t="n">
-        <v>-3.1045</v>
+        <v>2.1344</v>
       </c>
       <c r="Q13" t="n">
-        <v>-35.1199</v>
+        <v>-40.9411</v>
       </c>
       <c r="R13" t="n">
-        <v>32.0156</v>
+        <v>43.0752</v>
       </c>
       <c r="S13" t="n">
-        <v>-18.2479</v>
+        <v>-12.5104</v>
       </c>
       <c r="T13" t="n">
-        <v>-17.1328</v>
+        <v>-7.9165</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.1158</v>
+        <v>-4.5938</v>
       </c>
       <c r="V13" t="n">
-        <v>2.854</v>
+        <v>-4.721900000000001</v>
       </c>
       <c r="W13" t="n">
-        <v>17.1301</v>
+        <v>8.988</v>
       </c>
       <c r="X13" t="n">
-        <v>-14.276</v>
+        <v>-13.7097</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>E. VIDAL RODRIGUEZ</t>
+          <t>D. VAZQUEZ JEREZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D14" t="n">
-        <v>-27.2368</v>
+        <v>-20.7967</v>
       </c>
       <c r="E14" t="n">
-        <v>-19.6094</v>
+        <v>-22.8948</v>
       </c>
       <c r="F14" t="n">
-        <v>-7.6269</v>
+        <v>2.0977</v>
       </c>
       <c r="G14" t="n">
-        <v>-3.9633</v>
+        <v>-20.7961</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.2861</v>
+        <v>-1.3389</v>
       </c>
       <c r="I14" t="n">
-        <v>-2.6771</v>
+        <v>-19.4574</v>
       </c>
       <c r="J14" t="n">
-        <v>5.3716</v>
+        <v>2.158799999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>6.224600000000001</v>
+        <v>8.0124</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.8528000000000002</v>
+        <v>-5.853800000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>-9.3346</v>
+        <v>-22.9544</v>
       </c>
       <c r="N14" t="n">
-        <v>-7.5103</v>
+        <v>-9.351099999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.8242</v>
+        <v>-13.6031</v>
       </c>
       <c r="P14" t="n">
-        <v>-2.9105</v>
+        <v>3.6864</v>
       </c>
       <c r="Q14" t="n">
-        <v>-20.5675</v>
+        <v>-29.299</v>
       </c>
       <c r="R14" t="n">
-        <v>17.6571</v>
+        <v>32.9854</v>
       </c>
       <c r="S14" t="n">
-        <v>-9.3004</v>
+        <v>1.5432</v>
       </c>
       <c r="T14" t="n">
-        <v>-5.2121</v>
+        <v>-0.7363</v>
       </c>
       <c r="U14" t="n">
-        <v>-4.088</v>
+        <v>2.2789</v>
       </c>
       <c r="V14" t="n">
-        <v>-11.0628</v>
+        <v>-5.2301</v>
       </c>
       <c r="W14" t="n">
-        <v>0.7985</v>
+        <v>4.982100000000001</v>
       </c>
       <c r="X14" t="n">
-        <v>-11.8613</v>
+        <v>-10.2122</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>P. SÁNCHEZ GUTIERREZ</t>
+          <t>E. VIDAL RODRIGUEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>26</v>
       </c>
       <c r="D15" t="n">
-        <v>-29.9544</v>
+        <v>-22.949</v>
       </c>
       <c r="E15" t="n">
-        <v>-20.4036</v>
+        <v>-17.9028</v>
       </c>
       <c r="F15" t="n">
-        <v>-9.551000000000002</v>
+        <v>-5.0464</v>
       </c>
       <c r="G15" t="n">
-        <v>1.0546</v>
+        <v>-3.9633</v>
       </c>
       <c r="H15" t="n">
-        <v>7.057799999999999</v>
+        <v>-1.2861</v>
       </c>
       <c r="I15" t="n">
-        <v>-6.0031</v>
+        <v>-2.6771</v>
       </c>
       <c r="J15" t="n">
-        <v>30.363</v>
+        <v>5.3716</v>
       </c>
       <c r="K15" t="n">
-        <v>23.1633</v>
+        <v>6.224600000000001</v>
       </c>
       <c r="L15" t="n">
-        <v>7.199800000000001</v>
+        <v>-0.8528000000000002</v>
       </c>
       <c r="M15" t="n">
-        <v>-29.3085</v>
+        <v>-9.3346</v>
       </c>
       <c r="N15" t="n">
-        <v>-16.1055</v>
+        <v>-7.5103</v>
       </c>
       <c r="O15" t="n">
-        <v>-13.2028</v>
+        <v>-1.8242</v>
       </c>
       <c r="P15" t="n">
-        <v>2.1344</v>
+        <v>-2.9105</v>
       </c>
       <c r="Q15" t="n">
-        <v>-40.9411</v>
+        <v>-20.5675</v>
       </c>
       <c r="R15" t="n">
-        <v>43.0752</v>
+        <v>17.6571</v>
       </c>
       <c r="S15" t="n">
-        <v>-28.4218</v>
+        <v>-5.0125</v>
       </c>
       <c r="T15" t="n">
-        <v>-18.8141</v>
+        <v>-3.5055</v>
       </c>
       <c r="U15" t="n">
-        <v>-9.607799999999999</v>
+        <v>-1.507</v>
       </c>
       <c r="V15" t="n">
-        <v>-4.721900000000001</v>
+        <v>-11.0628</v>
       </c>
       <c r="W15" t="n">
-        <v>8.988</v>
+        <v>0.7985</v>
       </c>
       <c r="X15" t="n">
-        <v>-13.7097</v>
+        <v>-11.8613</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. MARTIN GONZALEZ</t>
+          <t>I. MENCARA JIMENEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>26</v>
       </c>
       <c r="D16" t="n">
-        <v>-37.1192</v>
+        <v>-24.3202</v>
       </c>
       <c r="E16" t="n">
-        <v>-29.6971</v>
+        <v>-6.755800000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>-7.4217</v>
+        <v>-17.5645</v>
       </c>
       <c r="G16" t="n">
-        <v>-22.0873</v>
+        <v>-10.7816</v>
       </c>
       <c r="H16" t="n">
-        <v>-7.7765</v>
+        <v>8.566599999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>-14.3107</v>
+        <v>-19.3478</v>
       </c>
       <c r="J16" t="n">
-        <v>7.5591</v>
+        <v>22.8679</v>
       </c>
       <c r="K16" t="n">
-        <v>10.3852</v>
+        <v>22.2448</v>
       </c>
       <c r="L16" t="n">
-        <v>-2.825799999999999</v>
+        <v>0.6227000000000023</v>
       </c>
       <c r="M16" t="n">
-        <v>-29.6465</v>
+        <v>-33.6489</v>
       </c>
       <c r="N16" t="n">
-        <v>-18.162</v>
+        <v>-13.6784</v>
       </c>
       <c r="O16" t="n">
-        <v>-11.4845</v>
+        <v>-19.971</v>
       </c>
       <c r="P16" t="n">
-        <v>6.985100000000002</v>
+        <v>2.3285</v>
       </c>
       <c r="Q16" t="n">
-        <v>-40.747</v>
+        <v>-32.4035</v>
       </c>
       <c r="R16" t="n">
-        <v>47.7318</v>
+        <v>34.732</v>
       </c>
       <c r="S16" t="n">
-        <v>-16.4548</v>
+        <v>-10.1205</v>
       </c>
       <c r="T16" t="n">
-        <v>-13.2139</v>
+        <v>-6.8679</v>
       </c>
       <c r="U16" t="n">
-        <v>-3.2409</v>
+        <v>-3.2526</v>
       </c>
       <c r="V16" t="n">
-        <v>-5.561999999999999</v>
+        <v>-5.746600000000001</v>
       </c>
       <c r="W16" t="n">
-        <v>16.7042</v>
+        <v>9.647600000000001</v>
       </c>
       <c r="X16" t="n">
-        <v>-22.2661</v>
+        <v>-15.3945</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>I. MENCARA JIMENEZ</t>
+          <t>A. MARTIN GONZALEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>26</v>
       </c>
       <c r="D17" t="n">
-        <v>-39.5718</v>
+        <v>-27.9456</v>
       </c>
       <c r="E17" t="n">
-        <v>-16.4125</v>
+        <v>-23.7415</v>
       </c>
       <c r="F17" t="n">
-        <v>-23.1594</v>
+        <v>-4.203900000000001</v>
       </c>
       <c r="G17" t="n">
-        <v>-10.7816</v>
+        <v>-22.0873</v>
       </c>
       <c r="H17" t="n">
-        <v>8.566599999999999</v>
+        <v>-7.7765</v>
       </c>
       <c r="I17" t="n">
-        <v>-19.3478</v>
+        <v>-14.3107</v>
       </c>
       <c r="J17" t="n">
-        <v>22.8679</v>
+        <v>7.5591</v>
       </c>
       <c r="K17" t="n">
-        <v>22.2448</v>
+        <v>10.3852</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6227000000000023</v>
+        <v>-2.825799999999999</v>
       </c>
       <c r="M17" t="n">
-        <v>-33.6489</v>
+        <v>-29.6465</v>
       </c>
       <c r="N17" t="n">
-        <v>-13.6784</v>
+        <v>-18.162</v>
       </c>
       <c r="O17" t="n">
-        <v>-19.971</v>
+        <v>-11.4845</v>
       </c>
       <c r="P17" t="n">
-        <v>2.3285</v>
+        <v>6.985100000000002</v>
       </c>
       <c r="Q17" t="n">
-        <v>-32.4035</v>
+        <v>-40.747</v>
       </c>
       <c r="R17" t="n">
-        <v>34.732</v>
+        <v>47.7318</v>
       </c>
       <c r="S17" t="n">
-        <v>-25.372</v>
+        <v>-7.2814</v>
       </c>
       <c r="T17" t="n">
-        <v>-16.5248</v>
+        <v>-7.2584</v>
       </c>
       <c r="U17" t="n">
-        <v>-8.8476</v>
+        <v>-0.02300000000000022</v>
       </c>
       <c r="V17" t="n">
-        <v>-5.746600000000001</v>
+        <v>-5.561999999999999</v>
       </c>
       <c r="W17" t="n">
-        <v>9.647600000000001</v>
+        <v>16.7042</v>
       </c>
       <c r="X17" t="n">
-        <v>-15.3945</v>
+        <v>-22.2661</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>25</v>
       </c>
       <c r="D18" t="n">
-        <v>-43.8101</v>
+        <v>-35.3098</v>
       </c>
       <c r="E18" t="n">
-        <v>-35.1902</v>
+        <v>-28.7578</v>
       </c>
       <c r="F18" t="n">
-        <v>-8.620200000000001</v>
+        <v>-6.5523</v>
       </c>
       <c r="G18" t="n">
         <v>-8.297000000000001</v>
@@ -1858,13 +1858,13 @@
         <v>42.1049</v>
       </c>
       <c r="S18" t="n">
-        <v>-15.9147</v>
+        <v>-7.414199999999999</v>
       </c>
       <c r="T18" t="n">
-        <v>-12.773</v>
+        <v>-6.3407</v>
       </c>
       <c r="U18" t="n">
-        <v>-3.1416</v>
+        <v>-1.0737</v>
       </c>
       <c r="V18" t="n">
         <v>-8.733000000000001</v>
@@ -1891,16 +1891,16 @@
         <v>26</v>
       </c>
       <c r="D19" t="n">
-        <v>-172.3008</v>
+        <v>-152.1733</v>
       </c>
       <c r="E19" t="n">
-        <v>-95.36300000000003</v>
+        <v>-86.5808</v>
       </c>
       <c r="F19" t="n">
-        <v>-76.93729999999999</v>
+        <v>-65.5925</v>
       </c>
       <c r="G19" t="n">
-        <v>-80.81379999999999</v>
+        <v>-80.8138</v>
       </c>
       <c r="H19" t="n">
         <v>28.547</v>
@@ -1915,7 +1915,7 @@
         <v>160.1479</v>
       </c>
       <c r="L19" t="n">
-        <v>22.0026</v>
+        <v>22.00260000000001</v>
       </c>
       <c r="M19" t="n">
         <v>-262.9621</v>
@@ -1936,16 +1936,16 @@
         <v>376.4229</v>
       </c>
       <c r="S19" t="n">
-        <v>-59.17989999999999</v>
+        <v>-39.0529</v>
       </c>
       <c r="T19" t="n">
-        <v>-46.02549999999999</v>
+        <v>-37.2435</v>
       </c>
       <c r="U19" t="n">
-        <v>-13.1557</v>
+        <v>-1.8102</v>
       </c>
       <c r="V19" t="n">
-        <v>-28.4272</v>
+        <v>-28.42720000000001</v>
       </c>
       <c r="W19" t="n">
         <v>148.815</v>
